--- a/2026--TSOSI-data-schema-infra-template.xlsx
+++ b/2026--TSOSI-data-schema-infra-template.xlsx
@@ -5,14 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Transfers" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Fields documentation" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Transfers!$A$1:$I$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Transfers!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t xml:space="preserve">institution/name</t>
   </si>
@@ -53,6 +53,9 @@
     <t xml:space="preserve">contract/date_end</t>
   </si>
   <si>
+    <t xml:space="preserve">support_type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Field</t>
   </si>
   <si>
@@ -84,6 +87,9 @@
   </si>
   <si>
     <t xml:space="preserve">If any, the end date of the contract. It usually to the start date of the support agreement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of support. Choose between : sponsorship, membership, service fee, grant or project funding, support, collaboration agreement, donation or other.</t>
   </si>
   <si>
     <t xml:space="preserve">Dates</t>
@@ -171,10 +177,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -199,13 +206,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -297,23 +297,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -321,7 +321,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -329,7 +329,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -542,14 +542,15 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="19.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="20.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="17.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="2" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="19.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="17.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.3"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="21.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="21.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -577,7 +578,9 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
@@ -591,6 +594,19 @@
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
     </row>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -606,7 +622,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:I42"/>
+  <autoFilter ref="A1:J1"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -627,25 +643,25 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="82.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="82.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="49.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -656,11 +672,11 @@
       <c r="J2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>12</v>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -671,11 +687,11 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>13</v>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -686,11 +702,11 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>14</v>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -705,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -720,7 +736,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -735,7 +751,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -746,11 +762,11 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>18</v>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -761,11 +777,11 @@
       <c r="J9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>19</v>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -775,7 +791,13 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -831,10 +853,10 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -847,7 +869,7 @@
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
       <c r="B18" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -859,7 +881,7 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13"/>
-      <c r="B19" s="8"/>
+      <c r="B19" s="5"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -869,7 +891,7 @@
       <c r="J19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8"/>
+      <c r="B20" s="5"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
